--- a/public/qaoa-rqp/QuantumPortfolioOptimizer_demo_24.xlsx
+++ b/public/qaoa-rqp/QuantumPortfolioOptimizer_demo_24.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielhug/Downloads/qaoa rqp demo excels/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielhug/Library/Mobile Documents/com~apple~CloudDocs/Quantum Computing/qaoa rqp demo excels/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35255A8-F94B-DE4B-821F-41F735CBCF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56AE9297-3734-3942-9FF3-D03B805EC2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="56140" yWindow="18400" windowWidth="29400" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
@@ -1072,9 +1072,6 @@
     <xf numFmtId="4" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1087,9 +1084,12 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1401,20 +1401,20 @@
       </c>
     </row>
     <row r="3" spans="1:1" s="3" customFormat="1" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="19" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" s="22"/>
+      <c r="A5" s="21"/>
     </row>
     <row r="6" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="22" t="s">
         <v>253</v>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="11">
-        <v>250000</v>
+        <v>2500000</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>251</v>
@@ -8862,7 +8862,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="11">
-        <v>2500</v>
+        <v>2500000</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>36</v>
@@ -9009,7 +9009,7 @@
       <c r="B33">
         <v>0</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="23" t="s">
         <v>114</v>
       </c>
     </row>
@@ -9020,7 +9020,7 @@
       <c r="B34">
         <v>0</v>
       </c>
-      <c r="C34" s="19"/>
+      <c r="C34" s="23"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
@@ -9029,7 +9029,7 @@
       <c r="B35">
         <v>16</v>
       </c>
-      <c r="C35" s="19"/>
+      <c r="C35" s="23"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
@@ -9038,7 +9038,7 @@
       <c r="B36">
         <v>0</v>
       </c>
-      <c r="C36" s="19"/>
+      <c r="C36" s="23"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
@@ -9047,7 +9047,7 @@
       <c r="B37">
         <v>0</v>
       </c>
-      <c r="C37" s="19"/>
+      <c r="C37" s="23"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
@@ -9056,7 +9056,7 @@
       <c r="B38">
         <v>16</v>
       </c>
-      <c r="C38" s="19"/>
+      <c r="C38" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
